--- a/AAII_Financials/Quarterly/ENGIY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ENGIY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="92">
   <si>
     <t>ENGIY</t>
   </si>
@@ -656,74 +656,80 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="19" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -769,8 +775,14 @@
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -816,8 +828,14 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -863,8 +881,14 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -882,8 +906,10 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -929,8 +955,14 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -976,8 +1008,14 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1023,8 +1061,14 @@
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1070,8 +1114,14 @@
       <c r="Q15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1086,8 +1136,10 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1133,8 +1185,14 @@
       <c r="Q17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1180,8 +1238,14 @@
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1199,8 +1263,10 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1246,8 +1312,14 @@
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1293,8 +1365,14 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1340,8 +1418,14 @@
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1387,8 +1471,14 @@
       <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1434,8 +1524,14 @@
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1481,8 +1577,14 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1528,8 +1630,14 @@
       <c r="Q26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1575,8 +1683,14 @@
       <c r="Q27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1622,8 +1736,14 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1669,8 +1789,14 @@
       <c r="Q29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1716,8 +1842,14 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1763,8 +1895,14 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1810,8 +1948,14 @@
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1857,8 +2001,14 @@
       <c r="Q33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1904,8 +2054,14 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1951,60 +2107,72 @@
       <c r="Q35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2022,8 +2190,10 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2041,431 +2211,487 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>15465600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>15608200</v>
+      </c>
+      <c r="F41" s="3">
         <v>17033000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>17021000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>17611300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>16208400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>17525600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>18880200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>18615700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>18744200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>18324300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>17546600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>17157200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>17075200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>16639900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>15267700</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>720900</v>
+      </c>
+      <c r="E42" s="3">
+        <v>727500</v>
+      </c>
+      <c r="F42" s="3">
         <v>1007400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>1006700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>1093400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>1006300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>837600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>902300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>852900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>858800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>3977000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>3808200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>889700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>885500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>6376000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>5850200</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>29629800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>29903100</v>
+      </c>
+      <c r="F43" s="3">
         <v>35814300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>35789000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>26031700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>23958100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>46224200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>49797000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>22718300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>22875200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>44874500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>42969900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>41000000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>40804000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>64231100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>58934100</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3758700</v>
+      </c>
+      <c r="E44" s="3">
+        <v>3793400</v>
+      </c>
+      <c r="F44" s="3">
         <v>3348600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>3346200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>3713400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>3417600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>5239700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>5644700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>5569500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>5607900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>5905800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>5655200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>5909400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>5881100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>8704700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>7986900</v>
       </c>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>18218900</v>
+      </c>
+      <c r="E45" s="3">
+        <v>18386900</v>
+      </c>
+      <c r="F45" s="3">
         <v>11358500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>11350500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>19189700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>17661000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>12333600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>13286900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>39256400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>39527500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>10500700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>10055000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>18588400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>18499600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>15161900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>13911600</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>67793900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>68419200</v>
+      </c>
+      <c r="F46" s="3">
         <v>68561700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>68513400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>67639500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>62251400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>82160700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>88511000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>87012800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>87613600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>83582400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>80034900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>83544800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>83145400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>111113600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>101950400</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>16932500</v>
+      </c>
+      <c r="E47" s="3">
+        <v>17088700</v>
+      </c>
+      <c r="F47" s="3">
         <v>15510200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>15499200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>15096900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>13894300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>13309900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>14338600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>13901200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>13997200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>17999300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>17235400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>17526200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>17442400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>15289100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>14028200</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>90013700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>90844000</v>
+      </c>
+      <c r="F48" s="3">
         <v>76903800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>76849700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>74105700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>68202600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>66661100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>71813500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>64672700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>65119200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>64054400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>61335700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>61216200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>60923500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>59301100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>54410700</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>34436200</v>
+      </c>
+      <c r="E49" s="3">
+        <v>34753800</v>
+      </c>
+      <c r="F49" s="3">
         <v>24690600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>24673200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>24722300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>22752900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>22005400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>23706200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>23011900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>23170800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>23558100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>22558200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>22053500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>21948100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>21607400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>19825500</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2511,8 +2737,14 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2558,55 +2790,67 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7710500</v>
+      </c>
+      <c r="E52" s="3">
+        <v>7781600</v>
+      </c>
+      <c r="F52" s="3">
         <v>10284100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>10276900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>6151500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>5661500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>9951300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>10720500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>7713500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>7766700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>17734100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>16981400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>16395200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>16316800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>37937400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>34808800</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2652,55 +2896,67 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>224237400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>226305800</v>
+      </c>
+      <c r="F54" s="3">
         <v>198719000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>198579100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>193457400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>178046900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>196235600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>211403100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>211420800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>212880600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>215143100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>206011900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>209322100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>208321400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>251672500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>230917800</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2718,8 +2974,10 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2737,290 +2995,328 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>21188200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>21383600</v>
+      </c>
+      <c r="F57" s="3">
         <v>19007900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>18994500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>18413400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>16946600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>18751400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>20200800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>23673000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>23836400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>24526400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>23485400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>22736900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>22628200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>41856400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>38404600</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>16434400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>16586000</v>
+      </c>
+      <c r="F58" s="3">
         <v>13380300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>13370900</v>
       </c>
-      <c r="F58" s="3">
-        <v>12225500</v>
-      </c>
-      <c r="G58" s="3">
-        <v>11251600</v>
-      </c>
       <c r="H58" s="3">
+        <v>12173800</v>
+      </c>
+      <c r="I58" s="3">
+        <v>11204100</v>
+      </c>
+      <c r="J58" s="3">
         <v>9586900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>10327900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>8166700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>8223100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>10498500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>10052900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>9512000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>9466500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>13489400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>12376900</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>29914300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>30190200</v>
+      </c>
+      <c r="F59" s="3">
         <v>27667000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>27647500</v>
       </c>
-      <c r="F59" s="3">
-        <v>33126200</v>
-      </c>
-      <c r="G59" s="3">
-        <v>30487500</v>
-      </c>
       <c r="H59" s="3">
+        <v>33177900</v>
+      </c>
+      <c r="I59" s="3">
+        <v>30535000</v>
+      </c>
+      <c r="J59" s="3">
         <v>44387600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>47818400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>56235900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>56624200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>46244100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>44281300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>53816600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>53559300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>42227200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>38744900</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>67855600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>68481500</v>
+      </c>
+      <c r="F60" s="3">
         <v>63203000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>63158500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>63850900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>58764600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>75457100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>81289300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>88162400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>88771200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>84035600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>80468900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>88616800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>88193200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>100222300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>91957200</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>63717600</v>
+      </c>
+      <c r="E61" s="3">
+        <v>64305300</v>
+      </c>
+      <c r="F61" s="3">
         <v>51416000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>51379800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>49662900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>45706900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>44840000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>48305800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>44742300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>45051200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>42419600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>40619200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>34978200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>34811000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>30675400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>28145700</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>21535500</v>
+      </c>
+      <c r="E62" s="3">
+        <v>21734100</v>
+      </c>
+      <c r="F62" s="3">
         <v>23639800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>23623100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>22345300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>20565300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>26776100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>28845600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>26404200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>26586500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>42872800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>41053100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>36027300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>35855100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>71812500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>65890400</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3066,8 +3362,14 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3113,8 +3415,14 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3160,55 +3468,67 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>168487400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>170041500</v>
+      </c>
+      <c r="F66" s="3">
         <v>150779600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>150673500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>148453300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>136627800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>153314000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>165164000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>170740400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>171919300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>175656000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>168200700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>171398500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>170579100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>209687900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>192395600</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3226,8 +3546,10 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3273,8 +3595,14 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3320,8 +3648,14 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3367,8 +3701,14 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3414,8 +3754,14 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -3461,8 +3807,14 @@
       <c r="Q72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3508,8 +3860,14 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3555,8 +3913,14 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3602,55 +3966,67 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>45962500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>46386500</v>
+      </c>
+      <c r="F76" s="3">
         <v>38688500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>38661300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>36317100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>33424100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>35776000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>38541200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>34835500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>35076100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>33223200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>31813100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>31769700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>31617800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>36606800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>33588000</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3696,60 +4072,72 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3795,8 +4183,14 @@
       <c r="Q81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3814,55 +4208,63 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1513200</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1392700</v>
+      </c>
+      <c r="F83" s="3">
         <v>1356800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>1461600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>1343600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>1352900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>1380600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>1322000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>1303500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>1297300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>1266400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>1162000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>1153000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>1225300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>1256100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>1280100</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3908,8 +4310,14 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3955,8 +4363,14 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4002,8 +4416,14 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4049,8 +4469,14 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4096,55 +4522,67 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4074600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>4112200</v>
+      </c>
+      <c r="F89" s="3">
         <v>1173500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>1172700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-2040500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-1878000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>2158600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>2325500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>4807700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>4840900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>1985700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>1901500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>5198700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>5173800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>872100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>800200</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4162,55 +4600,63 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1796500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-1813100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-2251400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-2249800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-2015300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-1854700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-2773100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-2987400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-2157900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-2172800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-2348800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-2249200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-1680100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-1672100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-2157700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-1979800</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4256,8 +4702,14 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4303,55 +4755,67 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-9132300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-9216500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-2729200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-2727300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>2990600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>2752400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-3064500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-3301400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-2902600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-2922600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-4230100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-4050600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-2272900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-2262100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>1180400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>1083100</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4369,55 +4833,63 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>2189500</v>
+      </c>
+      <c r="E96" s="3">
+        <v>2209700</v>
+      </c>
+      <c r="F96" s="3">
         <v>319900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>319700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>2339400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>2153000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>266600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>287200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>1945800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>1959200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>273000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>261400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>1950300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>1941000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>207300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>190200</v>
       </c>
     </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4463,8 +4935,14 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4510,8 +4988,14 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4557,145 +5041,169 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4395600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>4436200</v>
+      </c>
+      <c r="F100" s="3">
         <v>1309100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>1308200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-1813300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-1668800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>684300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>737200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-1488800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-1499100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>2752800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>2636000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-2837900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-2824300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-1504800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-1380700</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-271300</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-249700</v>
+      </c>
+      <c r="F101" s="3">
         <v>-8800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-9500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>10200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>10200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-31500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-30200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-8700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-8700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-58200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-53400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>246700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>262200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>63700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>64900</v>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-554100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-559200</v>
+      </c>
+      <c r="F102" s="3">
         <v>-287100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-286900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-1134500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-1044100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-230400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-248200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>426400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>429400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>477000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>456700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>79100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>78800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>489500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>449100</v>
       </c>
     </row>
